--- a/r5-core-47-sample-organizations/StructureDefinition-at-core-ext-gender-administrativeGenderAddition.xlsx
+++ b/r5-core-47-sample-organizations/StructureDefinition-at-core-ext-gender-administrativeGenderAddition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-11T21:11:59+00:00</t>
+    <t>2026-10-13T04:23:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-47-sample-organizations/StructureDefinition-at-core-ext-gender-administrativeGenderAddition.xlsx
+++ b/r5-core-47-sample-organizations/StructureDefinition-at-core-ext-gender-administrativeGenderAddition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T04:23:07+00:00</t>
+    <t>2026-10-13T10:45:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
